--- a/excel_routes/route_TUU_CAI_threats.xlsx
+++ b/excel_routes/route_TUU_CAI_threats.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_260726_at_14.46\reports\excel_routes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_270726_at_12.25\reports\excel_routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A642D695-9F19-4630-A2FE-6AD88AF933B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48AE1793-6C85-4050-8887-382D921E330D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12972" yWindow="348" windowWidth="10068" windowHeight="10284" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="72">
   <si>
     <t>Date</t>
   </si>
@@ -60,100 +60,40 @@
     <t>Currency</t>
   </si>
   <si>
-    <t>28-JUL-26</t>
+    <t>30-JUL-26</t>
   </si>
   <si>
     <t>SM-326</t>
   </si>
   <si>
+    <t>Nile Air NP-208</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>SAR</t>
+  </si>
+  <si>
+    <t>01-SEP-26</t>
+  </si>
+  <si>
     <t>Nesma Airlines NE-123</t>
   </si>
   <si>
-    <t>LOW</t>
-  </si>
-  <si>
-    <t>SAR</t>
-  </si>
-  <si>
-    <t>Nile Air NP-208</t>
-  </si>
-  <si>
-    <t>30-JUL-26</t>
-  </si>
-  <si>
-    <t>31-JUL-26</t>
+    <t>03-SEP-26</t>
+  </si>
+  <si>
+    <t>04-SEP-26</t>
+  </si>
+  <si>
+    <t>Nile Air NP-308</t>
+  </si>
+  <si>
+    <t>Nile Air NP-108</t>
   </si>
   <si>
     <t>Nesma Airlines NE-121</t>
-  </si>
-  <si>
-    <t>Nile Air NP-108</t>
-  </si>
-  <si>
-    <t>01-AUG-26</t>
-  </si>
-  <si>
-    <t>04-AUG-26</t>
-  </si>
-  <si>
-    <t>06-AUG-26</t>
-  </si>
-  <si>
-    <t>07-AUG-26</t>
-  </si>
-  <si>
-    <t>Nile Air NP-308</t>
-  </si>
-  <si>
-    <t>08-AUG-26</t>
-  </si>
-  <si>
-    <t>11-AUG-26</t>
-  </si>
-  <si>
-    <t>13-AUG-26</t>
-  </si>
-  <si>
-    <t>14-AUG-26</t>
-  </si>
-  <si>
-    <t>15-AUG-26</t>
-  </si>
-  <si>
-    <t>18-AUG-26</t>
-  </si>
-  <si>
-    <t>20-AUG-26</t>
-  </si>
-  <si>
-    <t>21-AUG-26</t>
-  </si>
-  <si>
-    <t>22-AUG-26</t>
-  </si>
-  <si>
-    <t>25-AUG-26</t>
-  </si>
-  <si>
-    <t>27-AUG-26</t>
-  </si>
-  <si>
-    <t>Nile Air NP-118</t>
-  </si>
-  <si>
-    <t>28-AUG-26</t>
-  </si>
-  <si>
-    <t>29-AUG-26</t>
-  </si>
-  <si>
-    <t>01-SEP-26</t>
-  </si>
-  <si>
-    <t>03-SEP-26</t>
-  </si>
-  <si>
-    <t>04-SEP-26</t>
   </si>
   <si>
     <t>05-SEP-26</t>
@@ -697,7 +637,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K122"/>
+  <dimension ref="A1:K85"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -761,19 +701,19 @@
         <v>319</v>
       </c>
       <c r="E2" s="2">
-        <v>312</v>
+        <v>355</v>
       </c>
       <c r="F2" s="2">
-        <v>7</v>
+        <v>-36</v>
       </c>
       <c r="G2" s="2">
         <v>40</v>
       </c>
       <c r="H2" s="2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I2" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>14</v>
@@ -784,31 +724,31 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D3" s="2">
-        <v>319</v>
+        <v>397</v>
       </c>
       <c r="E3" s="2">
-        <v>312</v>
+        <v>437</v>
       </c>
       <c r="F3" s="2">
-        <v>7</v>
+        <v>-40</v>
       </c>
       <c r="G3" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H3" s="2">
         <v>30</v>
       </c>
       <c r="I3" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>14</v>
@@ -819,22 +759,22 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="D4" s="2">
-        <v>319</v>
+        <v>400</v>
       </c>
       <c r="E4" s="2">
-        <v>312</v>
+        <v>437</v>
       </c>
       <c r="F4" s="2">
-        <v>7</v>
+        <v>-37</v>
       </c>
       <c r="G4" s="2">
         <v>40</v>
@@ -854,31 +794,31 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D5" s="2">
-        <v>319</v>
+        <v>397</v>
       </c>
       <c r="E5" s="2">
-        <v>312</v>
+        <v>437</v>
       </c>
       <c r="F5" s="2">
-        <v>7</v>
+        <v>-40</v>
       </c>
       <c r="G5" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2">
         <v>30</v>
       </c>
       <c r="I5" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>14</v>
@@ -895,16 +835,16 @@
         <v>12</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D6" s="2">
-        <v>319</v>
+        <v>430</v>
       </c>
       <c r="E6" s="2">
-        <v>312</v>
+        <v>437</v>
       </c>
       <c r="F6" s="2">
-        <v>7</v>
+        <v>-7</v>
       </c>
       <c r="G6" s="2">
         <v>40</v>
@@ -924,7 +864,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
@@ -933,22 +873,22 @@
         <v>20</v>
       </c>
       <c r="D7" s="2">
-        <v>319</v>
+        <v>397</v>
       </c>
       <c r="E7" s="2">
-        <v>312</v>
+        <v>437</v>
       </c>
       <c r="F7" s="2">
-        <v>7</v>
+        <v>-40</v>
       </c>
       <c r="G7" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2">
         <v>30</v>
       </c>
       <c r="I7" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>14</v>
@@ -959,31 +899,31 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="D8" s="2">
-        <v>319</v>
+        <v>397</v>
       </c>
       <c r="E8" s="2">
-        <v>312</v>
+        <v>437</v>
       </c>
       <c r="F8" s="2">
-        <v>7</v>
+        <v>-40</v>
       </c>
       <c r="G8" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H8" s="2">
         <v>30</v>
       </c>
       <c r="I8" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>14</v>
@@ -994,22 +934,22 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="D9" s="2">
-        <v>319</v>
+        <v>430</v>
       </c>
       <c r="E9" s="2">
-        <v>312</v>
+        <v>437</v>
       </c>
       <c r="F9" s="2">
-        <v>7</v>
+        <v>-7</v>
       </c>
       <c r="G9" s="2">
         <v>40</v>
@@ -1029,31 +969,31 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D10" s="2">
-        <v>319</v>
+        <v>397</v>
       </c>
       <c r="E10" s="2">
-        <v>312</v>
+        <v>402</v>
       </c>
       <c r="F10" s="2">
-        <v>7</v>
+        <v>-5</v>
       </c>
       <c r="G10" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H10" s="2">
         <v>30</v>
       </c>
       <c r="I10" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>14</v>
@@ -1070,16 +1010,16 @@
         <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D11" s="2">
-        <v>319</v>
+        <v>400</v>
       </c>
       <c r="E11" s="2">
-        <v>312</v>
+        <v>402</v>
       </c>
       <c r="F11" s="2">
-        <v>7</v>
+        <v>-2</v>
       </c>
       <c r="G11" s="2">
         <v>40</v>
@@ -1099,31 +1039,31 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D12" s="2">
-        <v>319</v>
+        <v>397</v>
       </c>
       <c r="E12" s="2">
-        <v>312</v>
+        <v>402</v>
       </c>
       <c r="F12" s="2">
-        <v>7</v>
+        <v>-5</v>
       </c>
       <c r="G12" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H12" s="2">
         <v>30</v>
       </c>
       <c r="I12" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>14</v>
@@ -1140,16 +1080,16 @@
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D13" s="2">
-        <v>319</v>
+        <v>400</v>
       </c>
       <c r="E13" s="2">
-        <v>312</v>
+        <v>402</v>
       </c>
       <c r="F13" s="2">
-        <v>7</v>
+        <v>-2</v>
       </c>
       <c r="G13" s="2">
         <v>40</v>
@@ -1169,31 +1109,31 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D14" s="2">
-        <v>319</v>
+        <v>397</v>
       </c>
       <c r="E14" s="2">
-        <v>312</v>
+        <v>402</v>
       </c>
       <c r="F14" s="2">
-        <v>7</v>
+        <v>-5</v>
       </c>
       <c r="G14" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H14" s="2">
         <v>30</v>
       </c>
       <c r="I14" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>14</v>
@@ -1204,22 +1144,22 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D15" s="2">
-        <v>319</v>
+        <v>430</v>
       </c>
       <c r="E15" s="2">
-        <v>312</v>
+        <v>402</v>
       </c>
       <c r="F15" s="2">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="G15" s="2">
         <v>40</v>
@@ -1239,22 +1179,22 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D16" s="2">
-        <v>319</v>
+        <v>430</v>
       </c>
       <c r="E16" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F16" s="2">
-        <v>7</v>
+        <v>115</v>
       </c>
       <c r="G16" s="2">
         <v>40</v>
@@ -1280,16 +1220,16 @@
         <v>12</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D17" s="2">
-        <v>319</v>
+        <v>400</v>
       </c>
       <c r="E17" s="2">
-        <v>312</v>
+        <v>362</v>
       </c>
       <c r="F17" s="2">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="G17" s="2">
         <v>40</v>
@@ -1315,16 +1255,16 @@
         <v>12</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D18" s="2">
-        <v>319</v>
+        <v>400</v>
       </c>
       <c r="E18" s="2">
-        <v>312</v>
+        <v>362</v>
       </c>
       <c r="F18" s="2">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="G18" s="2">
         <v>40</v>
@@ -1344,22 +1284,22 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D19" s="2">
-        <v>319</v>
+        <v>430</v>
       </c>
       <c r="E19" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F19" s="2">
-        <v>7</v>
+        <v>115</v>
       </c>
       <c r="G19" s="2">
         <v>40</v>
@@ -1379,22 +1319,22 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D20" s="2">
-        <v>319</v>
+        <v>400</v>
       </c>
       <c r="E20" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F20" s="2">
-        <v>7</v>
+        <v>85</v>
       </c>
       <c r="G20" s="2">
         <v>40</v>
@@ -1414,22 +1354,22 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D21" s="2">
-        <v>319</v>
+        <v>400</v>
       </c>
       <c r="E21" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F21" s="2">
-        <v>7</v>
+        <v>85</v>
       </c>
       <c r="G21" s="2">
         <v>40</v>
@@ -1449,22 +1389,22 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D22" s="2">
-        <v>319</v>
+        <v>400</v>
       </c>
       <c r="E22" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F22" s="2">
-        <v>7</v>
+        <v>85</v>
       </c>
       <c r="G22" s="2">
         <v>40</v>
@@ -1484,22 +1424,22 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D23" s="2">
-        <v>319</v>
+        <v>400</v>
       </c>
       <c r="E23" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F23" s="2">
-        <v>7</v>
+        <v>85</v>
       </c>
       <c r="G23" s="2">
         <v>40</v>
@@ -1519,22 +1459,22 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D24" s="2">
-        <v>397</v>
+        <v>430</v>
       </c>
       <c r="E24" s="2">
-        <v>312</v>
+        <v>362</v>
       </c>
       <c r="F24" s="2">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="G24" s="2">
         <v>40</v>
@@ -1554,22 +1494,22 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D25" s="2">
-        <v>319</v>
+        <v>400</v>
       </c>
       <c r="E25" s="2">
-        <v>312</v>
+        <v>362</v>
       </c>
       <c r="F25" s="2">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="G25" s="2">
         <v>40</v>
@@ -1589,19 +1529,19 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D26" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E26" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F26" s="2">
         <v>85</v>
@@ -1624,31 +1564,31 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D27" s="2">
-        <v>397</v>
+        <v>319</v>
       </c>
       <c r="E27" s="2">
-        <v>312</v>
+        <v>402</v>
       </c>
       <c r="F27" s="2">
-        <v>85</v>
+        <v>-83</v>
       </c>
       <c r="G27" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H27" s="2">
         <v>30</v>
       </c>
       <c r="I27" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>14</v>
@@ -1659,31 +1599,31 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D28" s="2">
         <v>397</v>
       </c>
       <c r="E28" s="2">
-        <v>312</v>
+        <v>402</v>
       </c>
       <c r="F28" s="2">
-        <v>85</v>
+        <v>-5</v>
       </c>
       <c r="G28" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H28" s="2">
         <v>30</v>
       </c>
       <c r="I28" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>14</v>
@@ -1694,31 +1634,31 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D29" s="2">
-        <v>397</v>
+        <v>319</v>
       </c>
       <c r="E29" s="2">
-        <v>312</v>
+        <v>362</v>
       </c>
       <c r="F29" s="2">
-        <v>85</v>
+        <v>-43</v>
       </c>
       <c r="G29" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H29" s="2">
         <v>30</v>
       </c>
       <c r="I29" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>14</v>
@@ -1729,31 +1669,31 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D30" s="2">
-        <v>397</v>
+        <v>319</v>
       </c>
       <c r="E30" s="2">
-        <v>312</v>
+        <v>362</v>
       </c>
       <c r="F30" s="2">
-        <v>85</v>
+        <v>-43</v>
       </c>
       <c r="G30" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H30" s="2">
         <v>30</v>
       </c>
       <c r="I30" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>14</v>
@@ -1764,31 +1704,31 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D31" s="2">
-        <v>319</v>
+        <v>397</v>
       </c>
       <c r="E31" s="2">
-        <v>312</v>
+        <v>437</v>
       </c>
       <c r="F31" s="2">
-        <v>7</v>
+        <v>-40</v>
       </c>
       <c r="G31" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H31" s="2">
         <v>30</v>
       </c>
       <c r="I31" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J31" s="3" t="s">
         <v>14</v>
@@ -1799,31 +1739,31 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D32" s="2">
         <v>397</v>
       </c>
       <c r="E32" s="2">
-        <v>312</v>
+        <v>437</v>
       </c>
       <c r="F32" s="2">
-        <v>85</v>
+        <v>-40</v>
       </c>
       <c r="G32" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H32" s="2">
         <v>30</v>
       </c>
       <c r="I32" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>14</v>
@@ -1834,31 +1774,31 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D33" s="2">
         <v>397</v>
       </c>
       <c r="E33" s="2">
-        <v>312</v>
+        <v>437</v>
       </c>
       <c r="F33" s="2">
-        <v>85</v>
+        <v>-40</v>
       </c>
       <c r="G33" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H33" s="2">
         <v>30</v>
       </c>
       <c r="I33" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>14</v>
@@ -1869,34 +1809,34 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="D34" s="2">
-        <v>319</v>
+        <v>405</v>
       </c>
       <c r="E34" s="2">
-        <v>312</v>
+        <v>2660</v>
       </c>
       <c r="F34" s="2">
-        <v>7</v>
+        <v>-2255</v>
       </c>
       <c r="G34" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H34" s="2">
         <v>30</v>
       </c>
       <c r="I34" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>15</v>
@@ -1904,34 +1844,34 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D35" s="2">
-        <v>397</v>
+        <v>2050</v>
       </c>
       <c r="E35" s="2">
-        <v>312</v>
+        <v>2660</v>
       </c>
       <c r="F35" s="2">
-        <v>85</v>
+        <v>-610</v>
       </c>
       <c r="G35" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H35" s="2">
         <v>30</v>
       </c>
       <c r="I35" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>15</v>
@@ -1939,34 +1879,34 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D36" s="2">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="E36" s="2">
-        <v>312</v>
+        <v>2660</v>
       </c>
       <c r="F36" s="2">
-        <v>85</v>
+        <v>-2234</v>
       </c>
       <c r="G36" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H36" s="2">
         <v>30</v>
       </c>
       <c r="I36" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>15</v>
@@ -1974,34 +1914,34 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D37" s="2">
-        <v>397</v>
+        <v>2050</v>
       </c>
       <c r="E37" s="2">
-        <v>391</v>
+        <v>2660</v>
       </c>
       <c r="F37" s="2">
-        <v>6</v>
+        <v>-610</v>
       </c>
       <c r="G37" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H37" s="2">
         <v>30</v>
       </c>
       <c r="I37" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>15</v>
@@ -2009,34 +1949,34 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="D38" s="2">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="E38" s="2">
-        <v>391</v>
+        <v>2660</v>
       </c>
       <c r="F38" s="2">
-        <v>6</v>
+        <v>-2234</v>
       </c>
       <c r="G38" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H38" s="2">
         <v>30</v>
       </c>
       <c r="I38" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>15</v>
@@ -2044,34 +1984,34 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D39" s="2">
-        <v>397</v>
+        <v>2050</v>
       </c>
       <c r="E39" s="2">
-        <v>391</v>
+        <v>2660</v>
       </c>
       <c r="F39" s="2">
-        <v>6</v>
+        <v>-610</v>
       </c>
       <c r="G39" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H39" s="2">
         <v>30</v>
       </c>
       <c r="I39" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>15</v>
@@ -2079,34 +2019,34 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="D40" s="2">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="E40" s="2">
-        <v>437</v>
+        <v>2660</v>
       </c>
       <c r="F40" s="2">
-        <v>-40</v>
+        <v>-2255</v>
       </c>
       <c r="G40" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H40" s="2">
         <v>30</v>
       </c>
       <c r="I40" s="2">
-        <v>0</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
+      </c>
+      <c r="J40" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>15</v>
@@ -2114,34 +2054,34 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D41" s="2">
-        <v>400</v>
+        <v>2050</v>
       </c>
       <c r="E41" s="2">
-        <v>437</v>
+        <v>2660</v>
       </c>
       <c r="F41" s="2">
-        <v>-37</v>
+        <v>-610</v>
       </c>
       <c r="G41" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H41" s="2">
         <v>30</v>
       </c>
       <c r="I41" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="J41" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>15</v>
@@ -2149,34 +2089,34 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="D42" s="2">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="E42" s="2">
-        <v>437</v>
+        <v>2660</v>
       </c>
       <c r="F42" s="2">
-        <v>-40</v>
+        <v>-2234</v>
       </c>
       <c r="G42" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H42" s="2">
         <v>30</v>
       </c>
       <c r="I42" s="2">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>15</v>
@@ -2184,34 +2124,34 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D43" s="2">
-        <v>430</v>
+        <v>2050</v>
       </c>
       <c r="E43" s="2">
-        <v>437</v>
+        <v>2660</v>
       </c>
       <c r="F43" s="2">
-        <v>-7</v>
+        <v>-610</v>
       </c>
       <c r="G43" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H43" s="2">
         <v>30</v>
       </c>
       <c r="I43" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>15</v>
@@ -2219,34 +2159,34 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="D44" s="2">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="E44" s="2">
-        <v>437</v>
+        <v>2660</v>
       </c>
       <c r="F44" s="2">
-        <v>-40</v>
+        <v>-2234</v>
       </c>
       <c r="G44" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H44" s="2">
         <v>30</v>
       </c>
       <c r="I44" s="2">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K44" s="2" t="s">
         <v>15</v>
@@ -2254,22 +2194,22 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D45" s="2">
-        <v>397</v>
+        <v>2050</v>
       </c>
       <c r="E45" s="2">
-        <v>437</v>
+        <v>2660</v>
       </c>
       <c r="F45" s="2">
-        <v>-40</v>
+        <v>-610</v>
       </c>
       <c r="G45" s="2">
         <v>30</v>
@@ -2280,8 +2220,8 @@
       <c r="I45" s="2">
         <v>0</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>14</v>
+      <c r="J45" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>15</v>
@@ -2289,34 +2229,34 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="D46" s="2">
-        <v>430</v>
+        <v>405</v>
       </c>
       <c r="E46" s="2">
-        <v>437</v>
+        <v>2660</v>
       </c>
       <c r="F46" s="2">
-        <v>-7</v>
+        <v>-2255</v>
       </c>
       <c r="G46" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H46" s="2">
         <v>30</v>
       </c>
       <c r="I46" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>15</v>
@@ -2324,22 +2264,22 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D47" s="2">
-        <v>397</v>
+        <v>2050</v>
       </c>
       <c r="E47" s="2">
-        <v>402</v>
+        <v>2660</v>
       </c>
       <c r="F47" s="2">
-        <v>-5</v>
+        <v>-610</v>
       </c>
       <c r="G47" s="2">
         <v>30</v>
@@ -2350,8 +2290,8 @@
       <c r="I47" s="2">
         <v>0</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>14</v>
+      <c r="J47" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>15</v>
@@ -2359,34 +2299,34 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="D48" s="2">
-        <v>400</v>
+        <v>426</v>
       </c>
       <c r="E48" s="2">
-        <v>402</v>
+        <v>2660</v>
       </c>
       <c r="F48" s="2">
-        <v>-2</v>
+        <v>-2234</v>
       </c>
       <c r="G48" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H48" s="2">
         <v>30</v>
       </c>
       <c r="I48" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>15</v>
@@ -2394,22 +2334,22 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D49" s="2">
-        <v>397</v>
+        <v>2050</v>
       </c>
       <c r="E49" s="2">
-        <v>402</v>
+        <v>2660</v>
       </c>
       <c r="F49" s="2">
-        <v>-5</v>
+        <v>-610</v>
       </c>
       <c r="G49" s="2">
         <v>30</v>
@@ -2420,8 +2360,8 @@
       <c r="I49" s="2">
         <v>0</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>14</v>
+      <c r="J49" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>15</v>
@@ -2429,34 +2369,34 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="D50" s="2">
-        <v>400</v>
+        <v>426</v>
       </c>
       <c r="E50" s="2">
-        <v>402</v>
+        <v>2660</v>
       </c>
       <c r="F50" s="2">
-        <v>-2</v>
+        <v>-2234</v>
       </c>
       <c r="G50" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H50" s="2">
         <v>30</v>
       </c>
       <c r="I50" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>15</v>
@@ -2464,22 +2404,22 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D51" s="2">
-        <v>397</v>
+        <v>2050</v>
       </c>
       <c r="E51" s="2">
-        <v>402</v>
+        <v>2660</v>
       </c>
       <c r="F51" s="2">
-        <v>-5</v>
+        <v>-610</v>
       </c>
       <c r="G51" s="2">
         <v>30</v>
@@ -2490,8 +2430,8 @@
       <c r="I51" s="2">
         <v>0</v>
       </c>
-      <c r="J51" s="3" t="s">
-        <v>14</v>
+      <c r="J51" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>15</v>
@@ -2499,22 +2439,22 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="D52" s="2">
-        <v>430</v>
+        <v>630</v>
       </c>
       <c r="E52" s="2">
-        <v>402</v>
+        <v>2660</v>
       </c>
       <c r="F52" s="2">
-        <v>28</v>
+        <v>-2030</v>
       </c>
       <c r="G52" s="2">
         <v>40</v>
@@ -2525,8 +2465,8 @@
       <c r="I52" s="2">
         <v>-10</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>14</v>
+      <c r="J52" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K52" s="2" t="s">
         <v>15</v>
@@ -2534,34 +2474,34 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D53" s="2">
-        <v>430</v>
+        <v>2050</v>
       </c>
       <c r="E53" s="2">
-        <v>315</v>
+        <v>2660</v>
       </c>
       <c r="F53" s="2">
-        <v>115</v>
+        <v>-610</v>
       </c>
       <c r="G53" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H53" s="2">
         <v>30</v>
       </c>
       <c r="I53" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J53" s="3" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K53" s="2" t="s">
         <v>15</v>
@@ -2569,34 +2509,34 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="D54" s="2">
-        <v>400</v>
+        <v>426</v>
       </c>
       <c r="E54" s="2">
-        <v>362</v>
+        <v>2660</v>
       </c>
       <c r="F54" s="2">
-        <v>38</v>
+        <v>-2234</v>
       </c>
       <c r="G54" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H54" s="2">
         <v>30</v>
       </c>
       <c r="I54" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="J54" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K54" s="2" t="s">
         <v>15</v>
@@ -2604,34 +2544,34 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D55" s="2">
-        <v>400</v>
+        <v>2050</v>
       </c>
       <c r="E55" s="2">
-        <v>362</v>
+        <v>2660</v>
       </c>
       <c r="F55" s="2">
-        <v>38</v>
+        <v>-610</v>
       </c>
       <c r="G55" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H55" s="2">
         <v>30</v>
       </c>
       <c r="I55" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="J55" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K55" s="2" t="s">
         <v>15</v>
@@ -2639,34 +2579,34 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="D56" s="2">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="E56" s="2">
-        <v>315</v>
+        <v>2660</v>
       </c>
       <c r="F56" s="2">
-        <v>115</v>
+        <v>-2234</v>
       </c>
       <c r="G56" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H56" s="2">
         <v>30</v>
       </c>
       <c r="I56" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="J56" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K56" s="2" t="s">
         <v>15</v>
@@ -2674,34 +2614,34 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D57" s="2">
-        <v>400</v>
+        <v>2050</v>
       </c>
       <c r="E57" s="2">
-        <v>315</v>
+        <v>2660</v>
       </c>
       <c r="F57" s="2">
-        <v>85</v>
+        <v>-610</v>
       </c>
       <c r="G57" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H57" s="2">
         <v>30</v>
       </c>
       <c r="I57" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>15</v>
@@ -2709,34 +2649,34 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="D58" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="E58" s="2">
-        <v>315</v>
+        <v>2660</v>
       </c>
       <c r="F58" s="2">
-        <v>85</v>
+        <v>-2255</v>
       </c>
       <c r="G58" s="2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H58" s="2">
         <v>30</v>
       </c>
       <c r="I58" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
+      </c>
+      <c r="J58" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>15</v>
@@ -2744,34 +2684,34 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D59" s="2">
-        <v>400</v>
+        <v>2050</v>
       </c>
       <c r="E59" s="2">
-        <v>315</v>
+        <v>2660</v>
       </c>
       <c r="F59" s="2">
-        <v>85</v>
+        <v>-610</v>
       </c>
       <c r="G59" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H59" s="2">
         <v>30</v>
       </c>
       <c r="I59" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="J59" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K59" s="2" t="s">
         <v>15</v>
@@ -2779,34 +2719,34 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="D60" s="2">
-        <v>400</v>
+        <v>426</v>
       </c>
       <c r="E60" s="2">
-        <v>315</v>
+        <v>2660</v>
       </c>
       <c r="F60" s="2">
-        <v>85</v>
+        <v>-2234</v>
       </c>
       <c r="G60" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H60" s="2">
         <v>30</v>
       </c>
       <c r="I60" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="J60" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>15</v>
@@ -2814,34 +2754,34 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D61" s="2">
-        <v>430</v>
+        <v>2050</v>
       </c>
       <c r="E61" s="2">
-        <v>362</v>
+        <v>2660</v>
       </c>
       <c r="F61" s="2">
-        <v>68</v>
+        <v>-610</v>
       </c>
       <c r="G61" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H61" s="2">
         <v>30</v>
       </c>
       <c r="I61" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J61" s="3" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="J61" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K61" s="2" t="s">
         <v>15</v>
@@ -2849,34 +2789,34 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="D62" s="2">
-        <v>400</v>
+        <v>426</v>
       </c>
       <c r="E62" s="2">
-        <v>362</v>
+        <v>2660</v>
       </c>
       <c r="F62" s="2">
-        <v>38</v>
+        <v>-2234</v>
       </c>
       <c r="G62" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H62" s="2">
         <v>30</v>
       </c>
       <c r="I62" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="J62" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K62" s="2" t="s">
         <v>15</v>
@@ -2884,34 +2824,34 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D63" s="2">
-        <v>400</v>
+        <v>2050</v>
       </c>
       <c r="E63" s="2">
-        <v>315</v>
+        <v>2660</v>
       </c>
       <c r="F63" s="2">
-        <v>85</v>
+        <v>-610</v>
       </c>
       <c r="G63" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H63" s="2">
         <v>30</v>
       </c>
       <c r="I63" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J63" s="3" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="J63" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K63" s="2" t="s">
         <v>15</v>
@@ -2919,34 +2859,34 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="D64" s="2">
-        <v>319</v>
+        <v>405</v>
       </c>
       <c r="E64" s="2">
-        <v>402</v>
+        <v>2660</v>
       </c>
       <c r="F64" s="2">
-        <v>-83</v>
+        <v>-2255</v>
       </c>
       <c r="G64" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H64" s="2">
         <v>30</v>
       </c>
       <c r="I64" s="2">
-        <v>0</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
+      </c>
+      <c r="J64" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K64" s="2" t="s">
         <v>15</v>
@@ -2954,22 +2894,22 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D65" s="2">
-        <v>397</v>
+        <v>2050</v>
       </c>
       <c r="E65" s="2">
-        <v>402</v>
+        <v>2660</v>
       </c>
       <c r="F65" s="2">
-        <v>-5</v>
+        <v>-610</v>
       </c>
       <c r="G65" s="2">
         <v>30</v>
@@ -2980,8 +2920,8 @@
       <c r="I65" s="2">
         <v>0</v>
       </c>
-      <c r="J65" s="3" t="s">
-        <v>14</v>
+      <c r="J65" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K65" s="2" t="s">
         <v>15</v>
@@ -2989,34 +2929,34 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="D66" s="2">
-        <v>319</v>
+        <v>426</v>
       </c>
       <c r="E66" s="2">
-        <v>362</v>
+        <v>2660</v>
       </c>
       <c r="F66" s="2">
-        <v>-43</v>
+        <v>-2234</v>
       </c>
       <c r="G66" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H66" s="2">
         <v>30</v>
       </c>
       <c r="I66" s="2">
-        <v>0</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="J66" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>15</v>
@@ -3024,22 +2964,22 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D67" s="2">
-        <v>319</v>
+        <v>2050</v>
       </c>
       <c r="E67" s="2">
-        <v>362</v>
+        <v>2660</v>
       </c>
       <c r="F67" s="2">
-        <v>-43</v>
+        <v>-610</v>
       </c>
       <c r="G67" s="2">
         <v>30</v>
@@ -3050,8 +2990,8 @@
       <c r="I67" s="2">
         <v>0</v>
       </c>
-      <c r="J67" s="3" t="s">
-        <v>14</v>
+      <c r="J67" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K67" s="2" t="s">
         <v>15</v>
@@ -3059,34 +2999,34 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="D68" s="2">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="E68" s="2">
-        <v>437</v>
+        <v>2660</v>
       </c>
       <c r="F68" s="2">
-        <v>-40</v>
+        <v>-2234</v>
       </c>
       <c r="G68" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H68" s="2">
         <v>30</v>
       </c>
       <c r="I68" s="2">
-        <v>0</v>
-      </c>
-      <c r="J68" s="3" t="s">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="J68" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K68" s="2" t="s">
         <v>15</v>
@@ -3094,22 +3034,22 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D69" s="2">
-        <v>397</v>
+        <v>2050</v>
       </c>
       <c r="E69" s="2">
-        <v>437</v>
+        <v>2660</v>
       </c>
       <c r="F69" s="2">
-        <v>-40</v>
+        <v>-610</v>
       </c>
       <c r="G69" s="2">
         <v>30</v>
@@ -3120,8 +3060,8 @@
       <c r="I69" s="2">
         <v>0</v>
       </c>
-      <c r="J69" s="3" t="s">
-        <v>14</v>
+      <c r="J69" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K69" s="2" t="s">
         <v>15</v>
@@ -3129,34 +3069,34 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C70" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D70" s="2">
+        <v>405</v>
+      </c>
+      <c r="E70" s="2">
+        <v>2660</v>
+      </c>
+      <c r="F70" s="2">
+        <v>-2255</v>
+      </c>
+      <c r="G70" s="2">
         <v>20</v>
       </c>
-      <c r="D70" s="2">
-        <v>397</v>
-      </c>
-      <c r="E70" s="2">
-        <v>437</v>
-      </c>
-      <c r="F70" s="2">
-        <v>-40</v>
-      </c>
-      <c r="G70" s="2">
-        <v>30</v>
-      </c>
       <c r="H70" s="2">
         <v>30</v>
       </c>
       <c r="I70" s="2">
-        <v>0</v>
-      </c>
-      <c r="J70" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
+      </c>
+      <c r="J70" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>15</v>
@@ -3164,34 +3104,34 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="D71" s="2">
-        <v>406</v>
+        <v>2050</v>
       </c>
       <c r="E71" s="2">
         <v>2660</v>
       </c>
       <c r="F71" s="2">
-        <v>-2254</v>
+        <v>-610</v>
       </c>
       <c r="G71" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H71" s="2">
         <v>30</v>
       </c>
       <c r="I71" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>15</v>
@@ -3199,34 +3139,34 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="D72" s="2">
-        <v>2050</v>
+        <v>426</v>
       </c>
       <c r="E72" s="2">
         <v>2660</v>
       </c>
       <c r="F72" s="2">
-        <v>-610</v>
+        <v>-2234</v>
       </c>
       <c r="G72" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H72" s="2">
         <v>30</v>
       </c>
       <c r="I72" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>15</v>
@@ -3234,34 +3174,34 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="D73" s="2">
-        <v>426</v>
+        <v>2050</v>
       </c>
       <c r="E73" s="2">
         <v>2660</v>
       </c>
       <c r="F73" s="2">
-        <v>-2234</v>
+        <v>-610</v>
       </c>
       <c r="G73" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H73" s="2">
         <v>30</v>
       </c>
       <c r="I73" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="K73" s="2" t="s">
         <v>15</v>
@@ -3275,28 +3215,28 @@
         <v>12</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="D74" s="2">
-        <v>2050</v>
+        <v>426</v>
       </c>
       <c r="E74" s="2">
         <v>2660</v>
       </c>
       <c r="F74" s="2">
-        <v>-610</v>
+        <v>-2234</v>
       </c>
       <c r="G74" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H74" s="2">
         <v>30</v>
       </c>
       <c r="I74" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="K74" s="2" t="s">
         <v>15</v>
@@ -3304,34 +3244,34 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="D75" s="2">
-        <v>426</v>
+        <v>2050</v>
       </c>
       <c r="E75" s="2">
         <v>2660</v>
       </c>
       <c r="F75" s="2">
-        <v>-2234</v>
+        <v>-610</v>
       </c>
       <c r="G75" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H75" s="2">
         <v>30</v>
       </c>
       <c r="I75" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="K75" s="2" t="s">
         <v>15</v>
@@ -3339,34 +3279,34 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C76" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D76" s="2">
+        <v>405</v>
+      </c>
+      <c r="E76" s="2">
+        <v>2660</v>
+      </c>
+      <c r="F76" s="2">
+        <v>-2255</v>
+      </c>
+      <c r="G76" s="2">
         <v>20</v>
       </c>
-      <c r="D76" s="2">
-        <v>2050</v>
-      </c>
-      <c r="E76" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F76" s="2">
-        <v>-610</v>
-      </c>
-      <c r="G76" s="2">
-        <v>30</v>
-      </c>
       <c r="H76" s="2">
         <v>30</v>
       </c>
       <c r="I76" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="K76" s="2" t="s">
         <v>15</v>
@@ -3374,34 +3314,34 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="D77" s="2">
-        <v>633</v>
+        <v>2050</v>
       </c>
       <c r="E77" s="2">
         <v>2660</v>
       </c>
       <c r="F77" s="2">
-        <v>-2027</v>
+        <v>-610</v>
       </c>
       <c r="G77" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H77" s="2">
         <v>30</v>
       </c>
       <c r="I77" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="K77" s="2" t="s">
         <v>15</v>
@@ -3409,34 +3349,34 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="D78" s="2">
-        <v>2050</v>
+        <v>426</v>
       </c>
       <c r="E78" s="2">
         <v>2660</v>
       </c>
       <c r="F78" s="2">
-        <v>-610</v>
+        <v>-2234</v>
       </c>
       <c r="G78" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H78" s="2">
         <v>30</v>
       </c>
       <c r="I78" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="K78" s="2" t="s">
         <v>15</v>
@@ -3444,34 +3384,34 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="D79" s="2">
-        <v>426</v>
+        <v>2050</v>
       </c>
       <c r="E79" s="2">
         <v>2660</v>
       </c>
       <c r="F79" s="2">
-        <v>-2234</v>
+        <v>-610</v>
       </c>
       <c r="G79" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H79" s="2">
         <v>30</v>
       </c>
       <c r="I79" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="K79" s="2" t="s">
         <v>15</v>
@@ -3479,34 +3419,34 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="D80" s="2">
-        <v>2050</v>
+        <v>426</v>
       </c>
       <c r="E80" s="2">
         <v>2660</v>
       </c>
       <c r="F80" s="2">
-        <v>-610</v>
+        <v>-2234</v>
       </c>
       <c r="G80" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H80" s="2">
         <v>30</v>
       </c>
       <c r="I80" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>15</v>
@@ -3514,34 +3454,34 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="D81" s="2">
-        <v>426</v>
+        <v>2050</v>
       </c>
       <c r="E81" s="2">
         <v>2660</v>
       </c>
       <c r="F81" s="2">
-        <v>-2234</v>
+        <v>-610</v>
       </c>
       <c r="G81" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H81" s="2">
         <v>30</v>
       </c>
       <c r="I81" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="K81" s="2" t="s">
         <v>15</v>
@@ -3549,34 +3489,34 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C82" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D82" s="2">
+        <v>405</v>
+      </c>
+      <c r="E82" s="2">
+        <v>2660</v>
+      </c>
+      <c r="F82" s="2">
+        <v>-2255</v>
+      </c>
+      <c r="G82" s="2">
         <v>20</v>
       </c>
-      <c r="D82" s="2">
-        <v>2050</v>
-      </c>
-      <c r="E82" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F82" s="2">
-        <v>-610</v>
-      </c>
-      <c r="G82" s="2">
-        <v>30</v>
-      </c>
       <c r="H82" s="2">
         <v>30</v>
       </c>
       <c r="I82" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J82" s="4" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="K82" s="2" t="s">
         <v>15</v>
@@ -3584,34 +3524,34 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="D83" s="2">
-        <v>406</v>
+        <v>2050</v>
       </c>
       <c r="E83" s="2">
         <v>2660</v>
       </c>
       <c r="F83" s="2">
-        <v>-2254</v>
+        <v>-610</v>
       </c>
       <c r="G83" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H83" s="2">
         <v>30</v>
       </c>
       <c r="I83" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="K83" s="2" t="s">
         <v>15</v>
@@ -3619,34 +3559,34 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="D84" s="2">
-        <v>2050</v>
+        <v>426</v>
       </c>
       <c r="E84" s="2">
         <v>2660</v>
       </c>
       <c r="F84" s="2">
-        <v>-610</v>
+        <v>-2234</v>
       </c>
       <c r="G84" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H84" s="2">
         <v>30</v>
       </c>
       <c r="I84" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="K84" s="2" t="s">
         <v>15</v>
@@ -3654,1331 +3594,36 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="D85" s="2">
-        <v>426</v>
+        <v>2050</v>
       </c>
       <c r="E85" s="2">
         <v>2660</v>
       </c>
       <c r="F85" s="2">
-        <v>-2234</v>
+        <v>-610</v>
       </c>
       <c r="G85" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H85" s="2">
         <v>30</v>
       </c>
       <c r="I85" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A86" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D86" s="2">
-        <v>2050</v>
-      </c>
-      <c r="E86" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F86" s="2">
-        <v>-610</v>
-      </c>
-      <c r="G86" s="2">
-        <v>30</v>
-      </c>
-      <c r="H86" s="2">
-        <v>30</v>
-      </c>
-      <c r="I86" s="2">
-        <v>0</v>
-      </c>
-      <c r="J86" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K86" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A87" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D87" s="2">
-        <v>426</v>
-      </c>
-      <c r="E87" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F87" s="2">
-        <v>-2234</v>
-      </c>
-      <c r="G87" s="2">
-        <v>0</v>
-      </c>
-      <c r="H87" s="2">
-        <v>30</v>
-      </c>
-      <c r="I87" s="2">
-        <v>30</v>
-      </c>
-      <c r="J87" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K87" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A88" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D88" s="2">
-        <v>2050</v>
-      </c>
-      <c r="E88" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F88" s="2">
-        <v>-610</v>
-      </c>
-      <c r="G88" s="2">
-        <v>30</v>
-      </c>
-      <c r="H88" s="2">
-        <v>30</v>
-      </c>
-      <c r="I88" s="2">
-        <v>0</v>
-      </c>
-      <c r="J88" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K88" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A89" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D89" s="2">
-        <v>406</v>
-      </c>
-      <c r="E89" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F89" s="2">
-        <v>-2254</v>
-      </c>
-      <c r="G89" s="2">
-        <v>20</v>
-      </c>
-      <c r="H89" s="2">
-        <v>30</v>
-      </c>
-      <c r="I89" s="2">
-        <v>10</v>
-      </c>
-      <c r="J89" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K89" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A90" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D90" s="2">
-        <v>2050</v>
-      </c>
-      <c r="E90" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F90" s="2">
-        <v>-610</v>
-      </c>
-      <c r="G90" s="2">
-        <v>30</v>
-      </c>
-      <c r="H90" s="2">
-        <v>30</v>
-      </c>
-      <c r="I90" s="2">
-        <v>0</v>
-      </c>
-      <c r="J90" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K90" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A91" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D91" s="2">
-        <v>426</v>
-      </c>
-      <c r="E91" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F91" s="2">
-        <v>-2234</v>
-      </c>
-      <c r="G91" s="2">
-        <v>0</v>
-      </c>
-      <c r="H91" s="2">
-        <v>30</v>
-      </c>
-      <c r="I91" s="2">
-        <v>30</v>
-      </c>
-      <c r="J91" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K91" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A92" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D92" s="2">
-        <v>2050</v>
-      </c>
-      <c r="E92" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F92" s="2">
-        <v>-610</v>
-      </c>
-      <c r="G92" s="2">
-        <v>30</v>
-      </c>
-      <c r="H92" s="2">
-        <v>30</v>
-      </c>
-      <c r="I92" s="2">
-        <v>0</v>
-      </c>
-      <c r="J92" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K92" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A93" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D93" s="2">
-        <v>426</v>
-      </c>
-      <c r="E93" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F93" s="2">
-        <v>-2234</v>
-      </c>
-      <c r="G93" s="2">
-        <v>0</v>
-      </c>
-      <c r="H93" s="2">
-        <v>30</v>
-      </c>
-      <c r="I93" s="2">
-        <v>30</v>
-      </c>
-      <c r="J93" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K93" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A94" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D94" s="2">
-        <v>2050</v>
-      </c>
-      <c r="E94" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F94" s="2">
-        <v>-610</v>
-      </c>
-      <c r="G94" s="2">
-        <v>30</v>
-      </c>
-      <c r="H94" s="2">
-        <v>30</v>
-      </c>
-      <c r="I94" s="2">
-        <v>0</v>
-      </c>
-      <c r="J94" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K94" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A95" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D95" s="2">
-        <v>633</v>
-      </c>
-      <c r="E95" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F95" s="2">
-        <v>-2027</v>
-      </c>
-      <c r="G95" s="2">
-        <v>40</v>
-      </c>
-      <c r="H95" s="2">
-        <v>30</v>
-      </c>
-      <c r="I95" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J95" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K95" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A96" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D96" s="2">
-        <v>2050</v>
-      </c>
-      <c r="E96" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F96" s="2">
-        <v>-610</v>
-      </c>
-      <c r="G96" s="2">
-        <v>30</v>
-      </c>
-      <c r="H96" s="2">
-        <v>30</v>
-      </c>
-      <c r="I96" s="2">
-        <v>0</v>
-      </c>
-      <c r="J96" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K96" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A97" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D97" s="2">
-        <v>426</v>
-      </c>
-      <c r="E97" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F97" s="2">
-        <v>-2234</v>
-      </c>
-      <c r="G97" s="2">
-        <v>0</v>
-      </c>
-      <c r="H97" s="2">
-        <v>30</v>
-      </c>
-      <c r="I97" s="2">
-        <v>30</v>
-      </c>
-      <c r="J97" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K97" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A98" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D98" s="2">
-        <v>2050</v>
-      </c>
-      <c r="E98" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F98" s="2">
-        <v>-610</v>
-      </c>
-      <c r="G98" s="2">
-        <v>30</v>
-      </c>
-      <c r="H98" s="2">
-        <v>30</v>
-      </c>
-      <c r="I98" s="2">
-        <v>0</v>
-      </c>
-      <c r="J98" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K98" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A99" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D99" s="2">
-        <v>426</v>
-      </c>
-      <c r="E99" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F99" s="2">
-        <v>-2234</v>
-      </c>
-      <c r="G99" s="2">
-        <v>0</v>
-      </c>
-      <c r="H99" s="2">
-        <v>30</v>
-      </c>
-      <c r="I99" s="2">
-        <v>30</v>
-      </c>
-      <c r="J99" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K99" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A100" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D100" s="2">
-        <v>2050</v>
-      </c>
-      <c r="E100" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F100" s="2">
-        <v>-610</v>
-      </c>
-      <c r="G100" s="2">
-        <v>30</v>
-      </c>
-      <c r="H100" s="2">
-        <v>30</v>
-      </c>
-      <c r="I100" s="2">
-        <v>0</v>
-      </c>
-      <c r="J100" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K100" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A101" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D101" s="2">
-        <v>633</v>
-      </c>
-      <c r="E101" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F101" s="2">
-        <v>-2027</v>
-      </c>
-      <c r="G101" s="2">
-        <v>40</v>
-      </c>
-      <c r="H101" s="2">
-        <v>30</v>
-      </c>
-      <c r="I101" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J101" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K101" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A102" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D102" s="2">
-        <v>2050</v>
-      </c>
-      <c r="E102" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F102" s="2">
-        <v>-610</v>
-      </c>
-      <c r="G102" s="2">
-        <v>30</v>
-      </c>
-      <c r="H102" s="2">
-        <v>30</v>
-      </c>
-      <c r="I102" s="2">
-        <v>0</v>
-      </c>
-      <c r="J102" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K102" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A103" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D103" s="2">
-        <v>426</v>
-      </c>
-      <c r="E103" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F103" s="2">
-        <v>-2234</v>
-      </c>
-      <c r="G103" s="2">
-        <v>0</v>
-      </c>
-      <c r="H103" s="2">
-        <v>30</v>
-      </c>
-      <c r="I103" s="2">
-        <v>30</v>
-      </c>
-      <c r="J103" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K103" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A104" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D104" s="2">
-        <v>2050</v>
-      </c>
-      <c r="E104" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F104" s="2">
-        <v>-610</v>
-      </c>
-      <c r="G104" s="2">
-        <v>30</v>
-      </c>
-      <c r="H104" s="2">
-        <v>30</v>
-      </c>
-      <c r="I104" s="2">
-        <v>0</v>
-      </c>
-      <c r="J104" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K104" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A105" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D105" s="2">
-        <v>426</v>
-      </c>
-      <c r="E105" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F105" s="2">
-        <v>-2234</v>
-      </c>
-      <c r="G105" s="2">
-        <v>0</v>
-      </c>
-      <c r="H105" s="2">
-        <v>30</v>
-      </c>
-      <c r="I105" s="2">
-        <v>30</v>
-      </c>
-      <c r="J105" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K105" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A106" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D106" s="2">
-        <v>2050</v>
-      </c>
-      <c r="E106" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F106" s="2">
-        <v>-610</v>
-      </c>
-      <c r="G106" s="2">
-        <v>30</v>
-      </c>
-      <c r="H106" s="2">
-        <v>30</v>
-      </c>
-      <c r="I106" s="2">
-        <v>0</v>
-      </c>
-      <c r="J106" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K106" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A107" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D107" s="2">
-        <v>406</v>
-      </c>
-      <c r="E107" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F107" s="2">
-        <v>-2254</v>
-      </c>
-      <c r="G107" s="2">
-        <v>20</v>
-      </c>
-      <c r="H107" s="2">
-        <v>30</v>
-      </c>
-      <c r="I107" s="2">
-        <v>10</v>
-      </c>
-      <c r="J107" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K107" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A108" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D108" s="2">
-        <v>2050</v>
-      </c>
-      <c r="E108" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F108" s="2">
-        <v>-610</v>
-      </c>
-      <c r="G108" s="2">
-        <v>30</v>
-      </c>
-      <c r="H108" s="2">
-        <v>30</v>
-      </c>
-      <c r="I108" s="2">
-        <v>0</v>
-      </c>
-      <c r="J108" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K108" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A109" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B109" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D109" s="2">
-        <v>426</v>
-      </c>
-      <c r="E109" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F109" s="2">
-        <v>-2234</v>
-      </c>
-      <c r="G109" s="2">
-        <v>0</v>
-      </c>
-      <c r="H109" s="2">
-        <v>30</v>
-      </c>
-      <c r="I109" s="2">
-        <v>30</v>
-      </c>
-      <c r="J109" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K109" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A110" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D110" s="2">
-        <v>2050</v>
-      </c>
-      <c r="E110" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F110" s="2">
-        <v>-610</v>
-      </c>
-      <c r="G110" s="2">
-        <v>30</v>
-      </c>
-      <c r="H110" s="2">
-        <v>30</v>
-      </c>
-      <c r="I110" s="2">
-        <v>0</v>
-      </c>
-      <c r="J110" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K110" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A111" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B111" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D111" s="2">
-        <v>426</v>
-      </c>
-      <c r="E111" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F111" s="2">
-        <v>-2234</v>
-      </c>
-      <c r="G111" s="2">
-        <v>0</v>
-      </c>
-      <c r="H111" s="2">
-        <v>30</v>
-      </c>
-      <c r="I111" s="2">
-        <v>30</v>
-      </c>
-      <c r="J111" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K111" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A112" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D112" s="2">
-        <v>2050</v>
-      </c>
-      <c r="E112" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F112" s="2">
-        <v>-610</v>
-      </c>
-      <c r="G112" s="2">
-        <v>30</v>
-      </c>
-      <c r="H112" s="2">
-        <v>30</v>
-      </c>
-      <c r="I112" s="2">
-        <v>0</v>
-      </c>
-      <c r="J112" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K112" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A113" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D113" s="2">
-        <v>406</v>
-      </c>
-      <c r="E113" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F113" s="2">
-        <v>-2254</v>
-      </c>
-      <c r="G113" s="2">
-        <v>20</v>
-      </c>
-      <c r="H113" s="2">
-        <v>30</v>
-      </c>
-      <c r="I113" s="2">
-        <v>10</v>
-      </c>
-      <c r="J113" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K113" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A114" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D114" s="2">
-        <v>2050</v>
-      </c>
-      <c r="E114" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F114" s="2">
-        <v>-610</v>
-      </c>
-      <c r="G114" s="2">
-        <v>30</v>
-      </c>
-      <c r="H114" s="2">
-        <v>30</v>
-      </c>
-      <c r="I114" s="2">
-        <v>0</v>
-      </c>
-      <c r="J114" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K114" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A115" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D115" s="2">
-        <v>426</v>
-      </c>
-      <c r="E115" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F115" s="2">
-        <v>-2234</v>
-      </c>
-      <c r="G115" s="2">
-        <v>0</v>
-      </c>
-      <c r="H115" s="2">
-        <v>30</v>
-      </c>
-      <c r="I115" s="2">
-        <v>30</v>
-      </c>
-      <c r="J115" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K115" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A116" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D116" s="2">
-        <v>2050</v>
-      </c>
-      <c r="E116" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F116" s="2">
-        <v>-610</v>
-      </c>
-      <c r="G116" s="2">
-        <v>30</v>
-      </c>
-      <c r="H116" s="2">
-        <v>30</v>
-      </c>
-      <c r="I116" s="2">
-        <v>0</v>
-      </c>
-      <c r="J116" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K116" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A117" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D117" s="2">
-        <v>426</v>
-      </c>
-      <c r="E117" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F117" s="2">
-        <v>-2234</v>
-      </c>
-      <c r="G117" s="2">
-        <v>0</v>
-      </c>
-      <c r="H117" s="2">
-        <v>30</v>
-      </c>
-      <c r="I117" s="2">
-        <v>30</v>
-      </c>
-      <c r="J117" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K117" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A118" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D118" s="2">
-        <v>2050</v>
-      </c>
-      <c r="E118" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F118" s="2">
-        <v>-610</v>
-      </c>
-      <c r="G118" s="2">
-        <v>30</v>
-      </c>
-      <c r="H118" s="2">
-        <v>30</v>
-      </c>
-      <c r="I118" s="2">
-        <v>0</v>
-      </c>
-      <c r="J118" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K118" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A119" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D119" s="2">
-        <v>633</v>
-      </c>
-      <c r="E119" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F119" s="2">
-        <v>-2027</v>
-      </c>
-      <c r="G119" s="2">
-        <v>40</v>
-      </c>
-      <c r="H119" s="2">
-        <v>30</v>
-      </c>
-      <c r="I119" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J119" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K119" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A120" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D120" s="2">
-        <v>2050</v>
-      </c>
-      <c r="E120" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F120" s="2">
-        <v>-610</v>
-      </c>
-      <c r="G120" s="2">
-        <v>30</v>
-      </c>
-      <c r="H120" s="2">
-        <v>30</v>
-      </c>
-      <c r="I120" s="2">
-        <v>0</v>
-      </c>
-      <c r="J120" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K120" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A121" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D121" s="2">
-        <v>426</v>
-      </c>
-      <c r="E121" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F121" s="2">
-        <v>-2234</v>
-      </c>
-      <c r="G121" s="2">
-        <v>0</v>
-      </c>
-      <c r="H121" s="2">
-        <v>30</v>
-      </c>
-      <c r="I121" s="2">
-        <v>30</v>
-      </c>
-      <c r="J121" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K121" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A122" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D122" s="2">
-        <v>2050</v>
-      </c>
-      <c r="E122" s="2">
-        <v>2660</v>
-      </c>
-      <c r="F122" s="2">
-        <v>-610</v>
-      </c>
-      <c r="G122" s="2">
-        <v>30</v>
-      </c>
-      <c r="H122" s="2">
-        <v>30</v>
-      </c>
-      <c r="I122" s="2">
-        <v>0</v>
-      </c>
-      <c r="J122" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K122" s="2" t="s">
         <v>15</v>
       </c>
     </row>
